--- a/в бланки заводов/Останкино СЫР/OrderCheeseInForm/lib/DB.xlsx
+++ b/в бланки заводов/Останкино СЫР/OrderCheeseInForm/lib/DB.xlsx
@@ -1,37 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино СЫР\OrderCheeseInForm\lib\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\в бланки заводов\Останкино СЫР\OrderCheeseInForm\lib\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84C93000-4993-453F-B81C-D83DBAACDA11}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4993AE76-1235-43C8-83F2-DDFCD3D7A344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="98">
   <si>
     <t>SKU</t>
   </si>
@@ -301,6 +295,30 @@
   </si>
   <si>
     <t>Масло сливочное ПАПА МОЖЕТ 82.5%, фас. в фольгу, 180гр</t>
+  </si>
+  <si>
+    <t>Сыч/Прод Коровино Российский Оригин 50% ВЕС НОВАЯ (3,5 кг)  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>Сыч/Прод Коровино Тильзитер Оригин 50% ВЕС НОВАЯ (5 кг брус) СЗМЖ  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>Сыч/Прод Коровино Российский 50% 200г НОВАЯ СЗМЖ  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>Сыр Косичка сырная 45% 100г/8шт Папа Может Останкино</t>
+  </si>
+  <si>
+    <t>Сыр Косичка сырная 45% 100г/8шт ТМ Папа Может</t>
+  </si>
+  <si>
+    <t>4931  Сыр полутвердый "Купеческий" с ароматом топленого молока, с м.д.ж. 50% ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>Сыр полутвердый "Тильзитер" с массовой долей жира в пересчете на сухое вещество 45%. 1/5  Останкино</t>
+  </si>
+  <si>
+    <t>Сыр полутвердый "Тильзитер" с массовой долей жира в пересчете на сухое вещество 45%, брус из блока 1/5, пленка желтая, короб складной, весовой</t>
   </si>
 </sst>
 </file>
@@ -336,9 +354,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -619,7 +636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="98.140625" bestFit="1" customWidth="1"/>
@@ -930,7 +947,7 @@
       <c r="A16" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16">
         <v>8785242</v>
       </c>
       <c r="C16" t="s">
@@ -948,13 +965,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="1">
-        <v>8785204</v>
+        <v>95</v>
+      </c>
+      <c r="B17">
+        <v>8785242</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D17">
         <v>16.5</v>
@@ -968,73 +985,73 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" s="1">
-        <v>8444170</v>
+        <v>38</v>
+      </c>
+      <c r="B18">
+        <v>8785204</v>
       </c>
       <c r="C18" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D18">
-        <v>8</v>
+        <v>16.5</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F18">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>42</v>
-      </c>
-      <c r="B19" s="1">
-        <v>5522704</v>
+        <v>40</v>
+      </c>
+      <c r="B19">
+        <v>8444170</v>
       </c>
       <c r="C19" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E19" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>44</v>
-      </c>
-      <c r="B20" s="1">
-        <v>9988391</v>
+        <v>42</v>
+      </c>
+      <c r="B20">
+        <v>5522704</v>
       </c>
       <c r="C20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D20">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F20">
-        <v>0.14000000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>46</v>
-      </c>
-      <c r="B21" s="1">
-        <v>9988681</v>
+        <v>44</v>
+      </c>
+      <c r="B21">
+        <v>9988391</v>
       </c>
       <c r="C21" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D21">
         <v>16</v>
@@ -1043,58 +1060,58 @@
         <v>8</v>
       </c>
       <c r="F21">
-        <v>0.18</v>
+        <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>48</v>
-      </c>
-      <c r="B22" s="1">
-        <v>8785198</v>
+        <v>46</v>
+      </c>
+      <c r="B22">
+        <v>9988681</v>
       </c>
       <c r="C22" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D22">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="E22" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B23">
-        <v>8444187</v>
+        <v>8785198</v>
       </c>
       <c r="C23" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D23">
-        <v>6</v>
+        <v>16.5</v>
       </c>
       <c r="E23" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F23">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B24">
-        <v>8444194</v>
+        <v>8444187</v>
       </c>
       <c r="C24" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D24">
         <v>6</v>
@@ -1108,53 +1125,53 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>54</v>
-      </c>
-      <c r="B25" t="s">
-        <v>55</v>
+        <v>52</v>
+      </c>
+      <c r="B25">
+        <v>8444194</v>
       </c>
       <c r="C25" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D25">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>57</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
+      </c>
+      <c r="B26" t="s">
+        <v>55</v>
       </c>
       <c r="C26" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D26">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E26" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>60</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>61</v>
+        <v>92</v>
+      </c>
+      <c r="B27" t="s">
+        <v>55</v>
       </c>
       <c r="C27" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D27">
         <v>10</v>
@@ -1168,13 +1185,13 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>63</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>64</v>
+        <v>57</v>
+      </c>
+      <c r="B28" t="s">
+        <v>58</v>
       </c>
       <c r="C28" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D28">
         <v>15</v>
@@ -1188,113 +1205,113 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>66</v>
-      </c>
-      <c r="B29">
-        <v>9988377</v>
+        <v>90</v>
+      </c>
+      <c r="B29" t="s">
+        <v>58</v>
       </c>
       <c r="C29" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D29">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E29" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F29">
-        <v>0.14000000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>68</v>
-      </c>
-      <c r="B30">
-        <v>6948249</v>
+        <v>60</v>
+      </c>
+      <c r="B30" t="s">
+        <v>61</v>
       </c>
       <c r="C30" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D30">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
       </c>
       <c r="F30">
-        <v>0.82499999999999996</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>70</v>
-      </c>
-      <c r="B31">
-        <v>6948256</v>
+        <v>63</v>
+      </c>
+      <c r="B31" t="s">
+        <v>64</v>
       </c>
       <c r="C31" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D31">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E31" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F31">
-        <v>0.372</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>72</v>
-      </c>
-      <c r="B32">
-        <v>6948263</v>
+        <v>91</v>
+      </c>
+      <c r="B32" t="s">
+        <v>64</v>
       </c>
       <c r="C32" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D32">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E32" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F32">
-        <v>0.74399999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B33">
-        <v>6948270</v>
+        <v>9988377</v>
       </c>
       <c r="C33" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="D33">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
       </c>
       <c r="F33">
-        <v>0.372</v>
+        <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B34">
-        <v>6948287</v>
+        <v>6948249</v>
       </c>
       <c r="C34" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D34">
         <v>12</v>
@@ -1303,138 +1320,138 @@
         <v>8</v>
       </c>
       <c r="F34">
-        <v>0.74399999999999999</v>
+        <v>0.82499999999999996</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B35">
-        <v>8783323</v>
+        <v>6948256</v>
       </c>
       <c r="C35" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D35">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E35" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>0.372</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B36">
-        <v>8444927</v>
+        <v>6948263</v>
       </c>
       <c r="C36" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D36">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
       </c>
       <c r="F36">
-        <v>0.1</v>
+        <v>0.74399999999999999</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B37">
-        <v>1018950</v>
+        <v>6948270</v>
       </c>
       <c r="C37" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D37">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
       </c>
       <c r="F37">
-        <v>0.18</v>
+        <v>0.372</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B38">
-        <v>8445177</v>
+        <v>6948287</v>
       </c>
       <c r="C38" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="D38">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
       </c>
       <c r="F38">
-        <v>0.1</v>
+        <v>0.74399999999999999</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>82</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>61</v>
+        <v>78</v>
+      </c>
+      <c r="B39">
+        <v>8783323</v>
       </c>
       <c r="C39" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="D39">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E39" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F39">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B40">
-        <v>8786928</v>
+        <v>8444927</v>
       </c>
       <c r="C40" t="s">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="D40">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E40" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B41">
-        <v>1018967</v>
+        <v>1018950</v>
       </c>
       <c r="C41" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D41">
         <v>10</v>
@@ -1444,6 +1461,126 @@
       </c>
       <c r="F41">
         <v>0.18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>93</v>
+      </c>
+      <c r="B42">
+        <v>8445160</v>
+      </c>
+      <c r="C42" t="s">
+        <v>94</v>
+      </c>
+      <c r="D42">
+        <v>8</v>
+      </c>
+      <c r="E42" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>81</v>
+      </c>
+      <c r="B43">
+        <v>8445177</v>
+      </c>
+      <c r="C43" t="s">
+        <v>86</v>
+      </c>
+      <c r="D43">
+        <v>8</v>
+      </c>
+      <c r="E43" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>82</v>
+      </c>
+      <c r="B44" t="s">
+        <v>61</v>
+      </c>
+      <c r="C44" t="s">
+        <v>62</v>
+      </c>
+      <c r="D44">
+        <v>10</v>
+      </c>
+      <c r="E44" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>87</v>
+      </c>
+      <c r="B45">
+        <v>8786928</v>
+      </c>
+      <c r="C45" t="s">
+        <v>20</v>
+      </c>
+      <c r="D45">
+        <v>6</v>
+      </c>
+      <c r="E45" t="s">
+        <v>21</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>88</v>
+      </c>
+      <c r="B46">
+        <v>1018967</v>
+      </c>
+      <c r="C46" t="s">
+        <v>89</v>
+      </c>
+      <c r="D46">
+        <v>10</v>
+      </c>
+      <c r="E46" t="s">
+        <v>8</v>
+      </c>
+      <c r="F46">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>96</v>
+      </c>
+      <c r="B47">
+        <v>8785259</v>
+      </c>
+      <c r="C47" t="s">
+        <v>97</v>
+      </c>
+      <c r="D47">
+        <v>16.5</v>
+      </c>
+      <c r="E47" t="s">
+        <v>21</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/в бланки заводов/Останкино СЫР/OrderCheeseInForm/lib/DB.xlsx
+++ b/в бланки заводов/Останкино СЫР/OrderCheeseInForm/lib/DB.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\в бланки заводов\Останкино СЫР\OrderCheeseInForm\lib\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино СЫР\OrderCheeseInForm\lib\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4993AE76-1235-43C8-83F2-DDFCD3D7A344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67CA2058-A797-4F0A-BF9E-AE32A7736EA2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$F$47</definedName>
+  </definedNames>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="100">
   <si>
     <t>SKU</t>
   </si>
@@ -319,6 +322,12 @@
   </si>
   <si>
     <t>Сыр полутвердый "Тильзитер" с массовой долей жира в пересчете на сухое вещество 45%, брус из блока 1/5, пленка желтая, короб складной, весовой</t>
+  </si>
+  <si>
+    <t>Cыр Перлини копченый 40% 100гр (8шт)  Останкино</t>
+  </si>
+  <si>
+    <t>Сыр Перлини копченый 40% 100гр (8шт)</t>
   </si>
 </sst>
 </file>
@@ -636,7 +645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="98.140625" bestFit="1" customWidth="1"/>
@@ -1583,7 +1592,28 @@
         <v>1</v>
       </c>
     </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>98</v>
+      </c>
+      <c r="B48">
+        <v>8444910</v>
+      </c>
+      <c r="C48" t="s">
+        <v>99</v>
+      </c>
+      <c r="D48">
+        <v>8</v>
+      </c>
+      <c r="E48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48">
+        <v>0.1</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:F47" xr:uid="{96B3D912-A4FF-4C68-B7EA-D60AFD3DF898}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/в бланки заводов/Останкино СЫР/OrderCheeseInForm/lib/DB.xlsx
+++ b/в бланки заводов/Останкино СЫР/OrderCheeseInForm/lib/DB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино СЫР\OrderCheeseInForm\lib\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67CA2058-A797-4F0A-BF9E-AE32A7736EA2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C1DDAC9-EA04-4093-A162-FF6179BF2C24}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="102">
   <si>
     <t>SKU</t>
   </si>
@@ -279,9 +279,6 @@
     <t>Сыч/Прод Коровино Тильзитер 50% 200г НОВАЯ СЗМЖ  ОСТАНКИНО</t>
   </si>
   <si>
-    <t>Сыр полутвердый Российский, цилиндр, 1/4, пленка с логотипом ЮКМП, массовая доля жира в сухом веществе 50%</t>
-  </si>
-  <si>
     <t>Сыр Перлини со вкусом Васаби 40% 100гр (8шт)</t>
   </si>
   <si>
@@ -328,6 +325,15 @@
   </si>
   <si>
     <t>Сыр Перлини копченый 40% 100гр (8шт)</t>
+  </si>
+  <si>
+    <t>Сыр полутвердый Российский, цилиндр, 1/4, пленка, массовая доля жира в сухом веществе 50%</t>
+  </si>
+  <si>
+    <t>Плавленый сыр "Шоколадный" 30% 180гр Папа Может Останкино</t>
+  </si>
+  <si>
+    <t>Плавленый сыр "Шоколадный" 30% 180 гр ТМ "ПАПА МОЖЕТ"</t>
   </si>
 </sst>
 </file>
@@ -645,7 +651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="98.140625" bestFit="1" customWidth="1"/>
@@ -974,7 +980,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B17">
         <v>8785242</v>
@@ -1174,7 +1180,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B27" t="s">
         <v>55</v>
@@ -1214,7 +1220,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B29" t="s">
         <v>58</v>
@@ -1274,7 +1280,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B32" t="s">
         <v>64</v>
@@ -1420,10 +1426,10 @@
         <v>8783323</v>
       </c>
       <c r="C39" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="D39">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E39" t="s">
         <v>21</v>
@@ -1440,7 +1446,7 @@
         <v>8444927</v>
       </c>
       <c r="C40" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D40">
         <v>8</v>
@@ -1460,7 +1466,7 @@
         <v>1018950</v>
       </c>
       <c r="C41" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D41">
         <v>10</v>
@@ -1474,13 +1480,13 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B42">
         <v>8445160</v>
       </c>
       <c r="C42" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D42">
         <v>8</v>
@@ -1500,7 +1506,7 @@
         <v>8445177</v>
       </c>
       <c r="C43" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D43">
         <v>8</v>
@@ -1534,7 +1540,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B45">
         <v>8786928</v>
@@ -1554,13 +1560,13 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B46">
         <v>1018967</v>
       </c>
       <c r="C46" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D46">
         <v>10</v>
@@ -1574,13 +1580,13 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B47">
         <v>8785259</v>
       </c>
       <c r="C47" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D47">
         <v>16.5</v>
@@ -1594,13 +1600,13 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B48">
         <v>8444910</v>
       </c>
       <c r="C48" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D48">
         <v>8</v>
@@ -1610,6 +1616,26 @@
       </c>
       <c r="F48">
         <v>0.1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>100</v>
+      </c>
+      <c r="B49">
+        <v>9988674</v>
+      </c>
+      <c r="C49" t="s">
+        <v>101</v>
+      </c>
+      <c r="D49">
+        <v>16</v>
+      </c>
+      <c r="E49" t="s">
+        <v>8</v>
+      </c>
+      <c r="F49">
+        <v>0.18</v>
       </c>
     </row>
   </sheetData>

--- a/в бланки заводов/Останкино СЫР/OrderCheeseInForm/lib/DB.xlsx
+++ b/в бланки заводов/Останкино СЫР/OrderCheeseInForm/lib/DB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино СЫР\OrderCheeseInForm\lib\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C1DDAC9-EA04-4093-A162-FF6179BF2C24}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4992E98B-5831-46FB-8036-2043C03B9154}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,19 +16,25 @@
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$F$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$F$49</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="103">
   <si>
     <t>SKU</t>
   </si>
@@ -334,6 +340,9 @@
   </si>
   <si>
     <t>Плавленый сыр "Шоколадный" 30% 180 гр ТМ "ПАПА МОЖЕТ"</t>
+  </si>
+  <si>
+    <t>Сыр полутвердый "Купеческий" с ароматом топленого молока, с массовой долей жира в пересчете на сухое вещество 50%, брус из блока 1/5, пленка желтая, короб складной ТМ "Папа может"</t>
   </si>
 </sst>
 </file>
@@ -349,12 +358,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -369,8 +390,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -651,14 +674,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="98.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="145.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -678,7 +701,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -697,8 +720,12 @@
       <c r="F2">
         <v>0.14000000000000001</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="b">
+        <f>COUNTIF(B:B,B2)&gt;1</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -717,8 +744,12 @@
       <c r="F3">
         <v>0.18</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="b">
+        <f t="shared" ref="G3:G49" si="0">COUNTIF(B:B,B3)&gt;1</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -737,8 +768,12 @@
       <c r="F4">
         <v>0.18</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -757,8 +792,12 @@
       <c r="F5">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -777,8 +816,12 @@
       <c r="F6">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -797,28 +840,36 @@
       <c r="F7">
         <v>0.18</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="2">
         <v>8786928</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="2">
         <v>6</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F8" s="2">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -837,8 +888,12 @@
       <c r="F9">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -857,8 +912,12 @@
       <c r="F10">
         <v>0.18</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -877,8 +936,12 @@
       <c r="F11">
         <v>0.18</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -897,8 +960,12 @@
       <c r="F12">
         <v>0.18</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -917,8 +984,12 @@
       <c r="F13">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -937,8 +1008,12 @@
       <c r="F14">
         <v>0.18</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -957,8 +1032,12 @@
       <c r="F15">
         <v>0.18</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -977,16 +1056,20 @@
       <c r="F16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>94</v>
       </c>
       <c r="B17">
-        <v>8785242</v>
+        <v>8784931</v>
       </c>
       <c r="C17" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D17">
         <v>16.5</v>
@@ -997,8 +1080,12 @@
       <c r="F17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>38</v>
       </c>
@@ -1017,8 +1104,12 @@
       <c r="F18">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -1037,8 +1128,12 @@
       <c r="F19">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -1057,8 +1152,12 @@
       <c r="F20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>44</v>
       </c>
@@ -1077,8 +1176,12 @@
       <c r="F21">
         <v>0.14000000000000001</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G21" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -1097,8 +1200,12 @@
       <c r="F22">
         <v>0.18</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G22" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -1117,8 +1224,12 @@
       <c r="F23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G23" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>50</v>
       </c>
@@ -1137,8 +1248,12 @@
       <c r="F24">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G24" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>52</v>
       </c>
@@ -1157,8 +1272,12 @@
       <c r="F25">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G25" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>54</v>
       </c>
@@ -1177,8 +1296,12 @@
       <c r="F26">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G26" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>91</v>
       </c>
@@ -1197,8 +1320,12 @@
       <c r="F27">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G27" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>57</v>
       </c>
@@ -1217,8 +1344,12 @@
       <c r="F28">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G28" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>89</v>
       </c>
@@ -1237,28 +1368,36 @@
       <c r="F29">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G29" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>60</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="1">
         <v>10</v>
       </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30">
+      <c r="E30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" s="1">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G30" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -1277,8 +1416,12 @@
       <c r="F31">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G31" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>90</v>
       </c>
@@ -1297,8 +1440,12 @@
       <c r="F32">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G32" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>66</v>
       </c>
@@ -1317,8 +1464,12 @@
       <c r="F33">
         <v>0.14000000000000001</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G33" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>68</v>
       </c>
@@ -1337,8 +1488,12 @@
       <c r="F34">
         <v>0.82499999999999996</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G34" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>70</v>
       </c>
@@ -1357,8 +1512,12 @@
       <c r="F35">
         <v>0.372</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G35" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>72</v>
       </c>
@@ -1377,8 +1536,12 @@
       <c r="F36">
         <v>0.74399999999999999</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G36" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>74</v>
       </c>
@@ -1397,8 +1560,12 @@
       <c r="F37">
         <v>0.372</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G37" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>76</v>
       </c>
@@ -1417,8 +1584,12 @@
       <c r="F38">
         <v>0.74399999999999999</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G38" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>78</v>
       </c>
@@ -1437,8 +1608,12 @@
       <c r="F39">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G39" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>79</v>
       </c>
@@ -1457,8 +1632,12 @@
       <c r="F40">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G40" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>80</v>
       </c>
@@ -1477,8 +1656,12 @@
       <c r="F41">
         <v>0.18</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G41" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>92</v>
       </c>
@@ -1497,8 +1680,12 @@
       <c r="F42">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G42" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>81</v>
       </c>
@@ -1517,48 +1704,60 @@
       <c r="F43">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G43" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>82</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="1">
         <v>10</v>
       </c>
-      <c r="E44" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44">
+      <c r="E44" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="1">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G44" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>86</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="2">
         <v>8786928</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="2">
         <v>6</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E45" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F45" s="2">
+        <v>1</v>
+      </c>
+      <c r="G45" s="2" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>87</v>
       </c>
@@ -1577,8 +1776,12 @@
       <c r="F46">
         <v>0.18</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G46" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>95</v>
       </c>
@@ -1597,8 +1800,12 @@
       <c r="F47">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G47" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>97</v>
       </c>
@@ -1617,8 +1824,12 @@
       <c r="F48">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G48" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>100</v>
       </c>
@@ -1637,9 +1848,13 @@
       <c r="F49">
         <v>0.18</v>
       </c>
+      <c r="G49" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F47" xr:uid="{96B3D912-A4FF-4C68-B7EA-D60AFD3DF898}"/>
+  <autoFilter ref="A1:F49" xr:uid="{96B3D912-A4FF-4C68-B7EA-D60AFD3DF898}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/в бланки заводов/Останкино СЫР/OrderCheeseInForm/lib/DB.xlsx
+++ b/в бланки заводов/Останкино СЫР/OrderCheeseInForm/lib/DB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино СЫР\OrderCheeseInForm\lib\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4992E98B-5831-46FB-8036-2043C03B9154}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15929EAE-CE0F-4F7A-9A5F-14DA88784830}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="107">
   <si>
     <t>SKU</t>
   </si>
@@ -343,6 +343,18 @@
   </si>
   <si>
     <t>Сыр полутвердый "Купеческий" с ароматом топленого молока, с массовой долей жира в пересчете на сухое вещество 50%, брус из блока 1/5, пленка желтая, короб складной ТМ "Папа может"</t>
+  </si>
+  <si>
+    <t>4421577 Спред растительно-сливочный "Сливочный вкус" 82,5% 180гр  Останкино</t>
+  </si>
+  <si>
+    <t>4421584 Спред растительно-сливочный "Сливочный вкус" 72,5% 180гр  Останкино</t>
+  </si>
+  <si>
+    <t>Спред растительно-сливочный «Сливочный вкус» 72,5% 180гр</t>
+  </si>
+  <si>
+    <t>Спред растительно-сливочный «Сливочный вкус» 82,5% 180гр</t>
   </si>
 </sst>
 </file>
@@ -674,7 +686,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="98.140625" bestFit="1" customWidth="1"/>
@@ -745,7 +757,7 @@
         <v>0.18</v>
       </c>
       <c r="G3" t="b">
-        <f t="shared" ref="G3:G49" si="0">COUNTIF(B:B,B3)&gt;1</f>
+        <f t="shared" ref="G3:G51" si="0">COUNTIF(B:B,B3)&gt;1</f>
         <v>0</v>
       </c>
     </row>
@@ -1849,6 +1861,54 @@
         <v>0.18</v>
       </c>
       <c r="G49" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>103</v>
+      </c>
+      <c r="B50">
+        <v>4421577</v>
+      </c>
+      <c r="C50" t="s">
+        <v>106</v>
+      </c>
+      <c r="D50">
+        <v>12</v>
+      </c>
+      <c r="E50" t="s">
+        <v>8</v>
+      </c>
+      <c r="F50">
+        <v>0.18</v>
+      </c>
+      <c r="G50" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>104</v>
+      </c>
+      <c r="B51">
+        <v>4421584</v>
+      </c>
+      <c r="C51" t="s">
+        <v>105</v>
+      </c>
+      <c r="D51">
+        <v>12</v>
+      </c>
+      <c r="E51" t="s">
+        <v>8</v>
+      </c>
+      <c r="F51">
+        <v>0.18</v>
+      </c>
+      <c r="G51" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>

--- a/в бланки заводов/Останкино СЫР/OrderCheeseInForm/lib/DB.xlsx
+++ b/в бланки заводов/Останкино СЫР/OrderCheeseInForm/lib/DB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино СЫР\OrderCheeseInForm\lib\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15929EAE-CE0F-4F7A-9A5F-14DA88784830}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9A11701-D33F-441B-A99E-CDD2CC42DEC0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$F$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$F$52</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="110">
   <si>
     <t>SKU</t>
   </si>
@@ -355,6 +355,15 @@
   </si>
   <si>
     <t>Спред растительно-сливочный «Сливочный вкус» 82,5% 180гр</t>
+  </si>
+  <si>
+    <t>Сыр полутвердый "Гауда" с массовой долей жира в пересчете на сухое вещество 45%,   Останкино</t>
+  </si>
+  <si>
+    <t>Сыр полутвердый "Голландский" с массовой долей жира в пересчете на сухое  Останкино</t>
+  </si>
+  <si>
+    <t>Сыр полутвердый "Голландский" с массовой долей жира в пересчете на сухое вещество 45%, брус из блока 1/5, пленка желтая, короб складной ТМ Папа может</t>
   </si>
 </sst>
 </file>
@@ -370,7 +379,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -389,6 +398,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -402,10 +417,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -686,7 +702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="98.140625" bestFit="1" customWidth="1"/>
@@ -733,7 +749,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="G2" t="b">
-        <f>COUNTIF(B:B,B2)&gt;1</f>
+        <f t="shared" ref="G2:G33" si="0">COUNTIF(B:B,B2)&gt;1</f>
         <v>0</v>
       </c>
     </row>
@@ -757,7 +773,7 @@
         <v>0.18</v>
       </c>
       <c r="G3" t="b">
-        <f t="shared" ref="G3:G51" si="0">COUNTIF(B:B,B3)&gt;1</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -883,46 +899,46 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9">
-        <v>8444163</v>
-      </c>
-      <c r="C9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9">
-        <v>8</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9">
-        <v>0.1</v>
-      </c>
-      <c r="G9" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>86</v>
+      </c>
+      <c r="B9" s="2">
+        <v>8786928</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="2">
+        <v>6</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B10">
-        <v>5038411</v>
+        <v>8444163</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="G10" t="b">
         <f t="shared" si="0"/>
@@ -931,13 +947,13 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B11">
-        <v>5038459</v>
+        <v>5038411</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -955,13 +971,13 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B12">
-        <v>5038831</v>
+        <v>5038459</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D12">
         <v>10</v>
@@ -979,13 +995,13 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B13">
-        <v>5038855</v>
+        <v>5038831</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D13">
         <v>10</v>
@@ -994,7 +1010,7 @@
         <v>8</v>
       </c>
       <c r="F13">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="G13" t="b">
         <f t="shared" si="0"/>
@@ -1003,13 +1019,13 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B14">
-        <v>5038435</v>
+        <v>5038855</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D14">
         <v>10</v>
@@ -1018,7 +1034,7 @@
         <v>8</v>
       </c>
       <c r="F14">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="G14" t="b">
         <f t="shared" si="0"/>
@@ -1027,13 +1043,13 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B15">
-        <v>5038398</v>
+        <v>5038435</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D15">
         <v>10</v>
@@ -1051,22 +1067,22 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B16">
-        <v>8785242</v>
+        <v>5038398</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D16">
-        <v>16.5</v>
+        <v>10</v>
       </c>
       <c r="E16" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>0.18</v>
       </c>
       <c r="G16" t="b">
         <f t="shared" si="0"/>
@@ -1075,70 +1091,70 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>94</v>
-      </c>
-      <c r="B17">
-        <v>8784931</v>
-      </c>
-      <c r="C17" t="s">
-        <v>102</v>
-      </c>
-      <c r="D17">
+        <v>36</v>
+      </c>
+      <c r="B17" s="3">
+        <v>8785242</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" s="3">
         <v>16.5</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F17">
-        <v>1</v>
-      </c>
-      <c r="G17" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="F17" s="3">
+        <v>1</v>
+      </c>
+      <c r="G17" s="3" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18">
-        <v>8785204</v>
-      </c>
-      <c r="C18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18">
+        <v>107</v>
+      </c>
+      <c r="B18" s="3">
+        <v>8785242</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="3">
         <v>16.5</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-      <c r="G18" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="F18" s="3">
+        <v>1</v>
+      </c>
+      <c r="G18" s="3" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="B19">
-        <v>8444170</v>
+        <v>8784931</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>102</v>
       </c>
       <c r="D19">
-        <v>8</v>
+        <v>16.5</v>
       </c>
       <c r="E19" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F19">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G19" t="b">
         <f t="shared" si="0"/>
@@ -1147,16 +1163,16 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B20">
-        <v>5522704</v>
+        <v>8785204</v>
       </c>
       <c r="C20" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D20">
-        <v>7</v>
+        <v>16.5</v>
       </c>
       <c r="E20" t="s">
         <v>21</v>
@@ -1171,22 +1187,22 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B21">
-        <v>9988391</v>
+        <v>8444170</v>
       </c>
       <c r="C21" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D21">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21">
-        <v>0.14000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="G21" t="b">
         <f t="shared" si="0"/>
@@ -1195,22 +1211,22 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B22">
-        <v>9988681</v>
+        <v>5522704</v>
       </c>
       <c r="C22" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D22">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E22" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F22">
-        <v>0.18</v>
+        <v>1</v>
       </c>
       <c r="G22" t="b">
         <f t="shared" si="0"/>
@@ -1219,22 +1235,22 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B23">
-        <v>8785198</v>
+        <v>9988391</v>
       </c>
       <c r="C23" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D23">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="E23" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G23" t="b">
         <f t="shared" si="0"/>
@@ -1243,22 +1259,22 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B24">
-        <v>8444187</v>
+        <v>9988681</v>
       </c>
       <c r="C24" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D24">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="G24" t="b">
         <f t="shared" si="0"/>
@@ -1267,22 +1283,22 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B25">
-        <v>8444194</v>
+        <v>8785198</v>
       </c>
       <c r="C25" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D25">
-        <v>6</v>
+        <v>16.5</v>
       </c>
       <c r="E25" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F25">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G25" t="b">
         <f t="shared" si="0"/>
@@ -1291,70 +1307,70 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>54</v>
-      </c>
-      <c r="B26" t="s">
-        <v>55</v>
+        <v>50</v>
+      </c>
+      <c r="B26">
+        <v>8444187</v>
       </c>
       <c r="C26" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="G26" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>91</v>
-      </c>
-      <c r="B27" t="s">
-        <v>55</v>
+        <v>52</v>
+      </c>
+      <c r="B27">
+        <v>8444194</v>
       </c>
       <c r="C27" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D27">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
       <c r="F27">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="G27" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C28" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D28">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E28" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="G28" t="b">
         <f t="shared" si="0"/>
@@ -1363,22 +1379,22 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C29" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D29">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E29" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="G29" t="b">
         <f t="shared" si="0"/>
@@ -1387,37 +1403,37 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>60</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D30" s="1">
-        <v>10</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="G30" s="1" t="b">
+        <v>57</v>
+      </c>
+      <c r="B30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" t="s">
+        <v>59</v>
+      </c>
+      <c r="D30">
+        <v>15</v>
+      </c>
+      <c r="E30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="B31" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C31" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D31">
         <v>15</v>
@@ -1435,133 +1451,133 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>90</v>
-      </c>
-      <c r="B32" t="s">
-        <v>64</v>
-      </c>
-      <c r="C32" t="s">
-        <v>65</v>
-      </c>
-      <c r="D32">
-        <v>15</v>
-      </c>
-      <c r="E32" t="s">
-        <v>21</v>
-      </c>
-      <c r="F32">
-        <v>1</v>
-      </c>
-      <c r="G32" t="b">
+        <v>60</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D32" s="1">
+        <v>10</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="G32" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>66</v>
-      </c>
-      <c r="B33">
-        <v>9988377</v>
-      </c>
-      <c r="C33" t="s">
-        <v>67</v>
-      </c>
-      <c r="D33">
-        <v>16</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="G33" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>82</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D33" s="1">
+        <v>10</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="G33" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>68</v>
-      </c>
-      <c r="B34">
-        <v>6948249</v>
+        <v>63</v>
+      </c>
+      <c r="B34" t="s">
+        <v>64</v>
       </c>
       <c r="C34" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D34">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E34" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F34">
-        <v>0.82499999999999996</v>
+        <v>1</v>
       </c>
       <c r="G34" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" ref="G34:G53" si="1">COUNTIF(B:B,B34)&gt;1</f>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>70</v>
-      </c>
-      <c r="B35">
-        <v>6948256</v>
+        <v>90</v>
+      </c>
+      <c r="B35" t="s">
+        <v>64</v>
       </c>
       <c r="C35" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D35">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E35" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F35">
-        <v>0.372</v>
+        <v>1</v>
       </c>
       <c r="G35" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B36">
-        <v>6948263</v>
+        <v>9988377</v>
       </c>
       <c r="C36" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D36">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
       </c>
       <c r="F36">
-        <v>0.74399999999999999</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G36" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B37">
-        <v>6948270</v>
+        <v>6948249</v>
       </c>
       <c r="C37" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D37">
         <v>12</v>
@@ -1570,22 +1586,22 @@
         <v>8</v>
       </c>
       <c r="F37">
-        <v>0.372</v>
+        <v>0.82499999999999996</v>
       </c>
       <c r="G37" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B38">
-        <v>6948287</v>
+        <v>6948256</v>
       </c>
       <c r="C38" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D38">
         <v>12</v>
@@ -1594,118 +1610,118 @@
         <v>8</v>
       </c>
       <c r="F38">
-        <v>0.74399999999999999</v>
+        <v>0.372</v>
       </c>
       <c r="G38" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B39">
-        <v>8783323</v>
+        <v>6948263</v>
       </c>
       <c r="C39" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="D39">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F39">
-        <v>1</v>
+        <v>0.74399999999999999</v>
       </c>
       <c r="G39" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B40">
-        <v>8444927</v>
+        <v>6948270</v>
       </c>
       <c r="C40" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D40">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
       </c>
       <c r="F40">
-        <v>0.1</v>
+        <v>0.372</v>
       </c>
       <c r="G40" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B41">
-        <v>1018950</v>
+        <v>6948287</v>
       </c>
       <c r="C41" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="D41">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
       </c>
       <c r="F41">
-        <v>0.18</v>
+        <v>0.74399999999999999</v>
       </c>
       <c r="G41" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="B42">
-        <v>8445160</v>
+        <v>8783323</v>
       </c>
       <c r="C42" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D42">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E42" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F42">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G42" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B43">
-        <v>8445177</v>
+        <v>8444927</v>
       </c>
       <c r="C43" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D43">
         <v>8</v>
@@ -1717,166 +1733,166 @@
         <v>0.1</v>
       </c>
       <c r="G43" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>82</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D44" s="1">
+        <v>80</v>
+      </c>
+      <c r="B44">
+        <v>1018950</v>
+      </c>
+      <c r="C44" t="s">
+        <v>84</v>
+      </c>
+      <c r="D44">
         <v>10</v>
       </c>
-      <c r="E44" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="G44" s="1" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="E44" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44">
+        <v>0.18</v>
+      </c>
+      <c r="G44" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>86</v>
-      </c>
-      <c r="B45" s="2">
-        <v>8786928</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D45" s="2">
-        <v>6</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F45" s="2">
-        <v>1</v>
-      </c>
-      <c r="G45" s="2" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>92</v>
+      </c>
+      <c r="B45">
+        <v>8445160</v>
+      </c>
+      <c r="C45" t="s">
+        <v>93</v>
+      </c>
+      <c r="D45">
+        <v>8</v>
+      </c>
+      <c r="E45" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45">
+        <v>0.1</v>
+      </c>
+      <c r="G45" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B46">
-        <v>1018967</v>
+        <v>8445177</v>
       </c>
       <c r="C46" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D46">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
       </c>
       <c r="F46">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="G46" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B47">
-        <v>8785259</v>
+        <v>1018967</v>
       </c>
       <c r="C47" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D47">
-        <v>16.5</v>
+        <v>10</v>
       </c>
       <c r="E47" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F47">
-        <v>1</v>
+        <v>0.18</v>
       </c>
       <c r="G47" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B48">
-        <v>8444910</v>
+        <v>8785259</v>
       </c>
       <c r="C48" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D48">
-        <v>8</v>
+        <v>16.5</v>
       </c>
       <c r="E48" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F48">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G48" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B49">
-        <v>9988674</v>
+        <v>8444910</v>
       </c>
       <c r="C49" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D49">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
       </c>
       <c r="F49">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="G49" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B50">
-        <v>4421577</v>
+        <v>9988674</v>
       </c>
       <c r="C50" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D50">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
@@ -1885,19 +1901,19 @@
         <v>0.18</v>
       </c>
       <c r="G50" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B51">
-        <v>4421584</v>
+        <v>4421577</v>
       </c>
       <c r="C51" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D51">
         <v>12</v>
@@ -1909,12 +1925,60 @@
         <v>0.18</v>
       </c>
       <c r="G51" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>104</v>
+      </c>
+      <c r="B52">
+        <v>4421584</v>
+      </c>
+      <c r="C52" t="s">
+        <v>105</v>
+      </c>
+      <c r="D52">
+        <v>12</v>
+      </c>
+      <c r="E52" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52">
+        <v>0.18</v>
+      </c>
+      <c r="G52" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>108</v>
+      </c>
+      <c r="B53">
+        <v>8785235</v>
+      </c>
+      <c r="C53" t="s">
+        <v>109</v>
+      </c>
+      <c r="D53">
+        <v>16.5</v>
+      </c>
+      <c r="E53" t="s">
+        <v>21</v>
+      </c>
+      <c r="F53">
+        <v>1</v>
+      </c>
+      <c r="G53" t="b">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F49" xr:uid="{96B3D912-A4FF-4C68-B7EA-D60AFD3DF898}"/>
+  <autoFilter ref="A1:F52" xr:uid="{96B3D912-A4FF-4C68-B7EA-D60AFD3DF898}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/в бланки заводов/Останкино СЫР/OrderCheeseInForm/lib/DB.xlsx
+++ b/в бланки заводов/Останкино СЫР/OrderCheeseInForm/lib/DB.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино СЫР\OrderCheeseInForm\lib\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\в бланки заводов\Останкино СЫР\OrderCheeseInForm\lib\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9A11701-D33F-441B-A99E-CDD2CC42DEC0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DFEEA8E-ED59-4F7D-8AA8-BC7840FC81B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,23 +18,17 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$F$52</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="116">
   <si>
     <t>SKU</t>
   </si>
@@ -364,6 +358,24 @@
   </si>
   <si>
     <t>Сыр полутвердый "Голландский" с массовой долей жира в пересчете на сухое вещество 45%, брус из блока 1/5, пленка желтая, короб складной ТМ Папа может</t>
+  </si>
+  <si>
+    <t>1103201 Сыр копченый "Косичка" мини ПАПА МОЖЕТ 55г лоток  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>2103201 БЖП, произведенный по технологии сыра копченый "Косичка" мини Ассорти  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>2105201 БЖП, произведенный по технологии сыра копченый "Балык" резаный 4 вкуса  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>БЖП, произведенный по технологии сыра копченый "Балык" резаный 4 вкуса</t>
+  </si>
+  <si>
+    <t>БЖП, произведенный по технологии сыра копченый "Косичка" мини Ассорти</t>
+  </si>
+  <si>
+    <t>Сыр копченый "Косичка" мини ПАПА МОЖЕТ 55г лоток</t>
   </si>
 </sst>
 </file>
@@ -702,7 +714,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="98.140625" bestFit="1" customWidth="1"/>
@@ -1517,7 +1529,7 @@
         <v>1</v>
       </c>
       <c r="G34" t="b">
-        <f t="shared" ref="G34:G53" si="1">COUNTIF(B:B,B34)&gt;1</f>
+        <f t="shared" ref="G34:G56" si="1">COUNTIF(B:B,B34)&gt;1</f>
         <v>1</v>
       </c>
     </row>
@@ -1973,6 +1985,78 @@
         <v>1</v>
       </c>
       <c r="G53" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>110</v>
+      </c>
+      <c r="B54">
+        <v>1103201</v>
+      </c>
+      <c r="C54" t="s">
+        <v>115</v>
+      </c>
+      <c r="D54">
+        <v>24</v>
+      </c>
+      <c r="E54" t="s">
+        <v>8</v>
+      </c>
+      <c r="F54">
+        <v>5.5E-2</v>
+      </c>
+      <c r="G54" t="b">
+        <f>COUNTIF(B:B,B55)&gt;1</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>111</v>
+      </c>
+      <c r="B55">
+        <v>2103201</v>
+      </c>
+      <c r="C55" t="s">
+        <v>114</v>
+      </c>
+      <c r="D55">
+        <v>24</v>
+      </c>
+      <c r="E55" t="s">
+        <v>8</v>
+      </c>
+      <c r="F55">
+        <v>0.1</v>
+      </c>
+      <c r="G55" t="b">
+        <f>COUNTIF(B:B,#REF!)&gt;1</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>112</v>
+      </c>
+      <c r="B56">
+        <v>2105201</v>
+      </c>
+      <c r="C56" t="s">
+        <v>113</v>
+      </c>
+      <c r="D56">
+        <v>24</v>
+      </c>
+      <c r="E56" t="s">
+        <v>8</v>
+      </c>
+      <c r="F56">
+        <v>0.1</v>
+      </c>
+      <c r="G56" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>

--- a/в бланки заводов/Останкино СЫР/OrderCheeseInForm/lib/DB.xlsx
+++ b/в бланки заводов/Останкино СЫР/OrderCheeseInForm/lib/DB.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\в бланки заводов\Останкино СЫР\OrderCheeseInForm\lib\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино СЫР\OrderCheeseInForm\lib\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DFEEA8E-ED59-4F7D-8AA8-BC7840FC81B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37CBADD7-8867-47FB-AC50-9B7986D97D77}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,19 +16,25 @@
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$F$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$F$59</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="122">
   <si>
     <t>SKU</t>
   </si>
@@ -376,19 +382,44 @@
   </si>
   <si>
     <t>Сыр копченый "Косичка" мини ПАПА МОЖЕТ 55г лоток</t>
+  </si>
+  <si>
+    <t>Продукт белково-жировой Сметанковый 50% вес ТМ Коровино</t>
+  </si>
+  <si>
+    <t>Продукт белково-жировой Сметанковый 50% ВЕС Коровино Останкино</t>
+  </si>
+  <si>
+    <t>Продукт По-Росийски Классический с ЗМЖ 50% 200г Коровино Останкино</t>
+  </si>
+  <si>
+    <t>Продукт По-Росийски Классический с ЗМЖ 50% ВЕС Коровино Останкино</t>
+  </si>
+  <si>
+    <t>Продукт По-Российски Классический с заменителем молочного жира мдж 50% 200г фасовка ТМ Коровино</t>
+  </si>
+  <si>
+    <t>Продукт По-Российски Классический с заменителем молочного жира мдж 50% ТМ Коровино</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0_ ;[Red]\-0\ "/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="5">
@@ -426,16 +457,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Arial10px" xfId="1" xr:uid="{848D5204-7CA3-438A-9585-1CC7452ED98C}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -714,7 +748,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="98.140625" bestFit="1" customWidth="1"/>
@@ -1529,7 +1563,7 @@
         <v>1</v>
       </c>
       <c r="G34" t="b">
-        <f t="shared" ref="G34:G56" si="1">COUNTIF(B:B,B34)&gt;1</f>
+        <f t="shared" ref="G34:G59" si="1">COUNTIF(B:B,B34)&gt;1</f>
         <v>1</v>
       </c>
     </row>
@@ -2061,8 +2095,80 @@
         <v>0</v>
       </c>
     </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>117</v>
+      </c>
+      <c r="B57">
+        <v>7100726</v>
+      </c>
+      <c r="C57" t="s">
+        <v>116</v>
+      </c>
+      <c r="D57">
+        <v>20</v>
+      </c>
+      <c r="E57" t="s">
+        <v>21</v>
+      </c>
+      <c r="F57">
+        <v>1</v>
+      </c>
+      <c r="G57" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B58">
+        <v>7100108</v>
+      </c>
+      <c r="C58" t="s">
+        <v>120</v>
+      </c>
+      <c r="D58">
+        <v>12</v>
+      </c>
+      <c r="E58" t="s">
+        <v>8</v>
+      </c>
+      <c r="F58">
+        <v>0.2</v>
+      </c>
+      <c r="G58" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B59">
+        <v>7100139</v>
+      </c>
+      <c r="C59" t="s">
+        <v>121</v>
+      </c>
+      <c r="D59">
+        <v>20</v>
+      </c>
+      <c r="E59" t="s">
+        <v>21</v>
+      </c>
+      <c r="F59">
+        <v>1</v>
+      </c>
+      <c r="G59" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F52" xr:uid="{96B3D912-A4FF-4C68-B7EA-D60AFD3DF898}"/>
+  <autoFilter ref="A1:F59" xr:uid="{96B3D912-A4FF-4C68-B7EA-D60AFD3DF898}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>